--- a/GoldfishMemory.xlsx
+++ b/GoldfishMemory.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manju\Desktop\Academia\website_portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0928EB53-6405-4FA7-A04B-27117BDCBF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF33FB4B-1A12-40DD-AC57-D00BA3FCC66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Neuroscience" sheetId="2" r:id="rId1"/>
-    <sheet name="Maths" sheetId="1" r:id="rId2"/>
+    <sheet name="Maths" sheetId="1" r:id="rId1"/>
+    <sheet name="Neuroscience" sheetId="2" r:id="rId2"/>
     <sheet name="Research methods" sheetId="3" r:id="rId3"/>
     <sheet name="Quiz" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
   <si>
     <t>Neuroscience</t>
   </si>
@@ -271,16 +271,106 @@
     <t>Fish</t>
   </si>
   <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Top score</t>
-  </si>
-  <si>
     <t>Outlier</t>
   </si>
   <si>
     <t xml:space="preserve">Z normalization </t>
+  </si>
+  <si>
+    <t>Z-score normalization/standardization, is crucial data preprocessing technique in machine learning and statistics. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Converts the data into unitless numbers. The new units are standard deviations away from the mean of the distribution. Z= X−μ/ σ </t>
+  </si>
+  <si>
+    <t>Why are outliers scary?</t>
+  </si>
+  <si>
+    <t>When squared, it makes huge variation and impact on the graph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is not scary. </t>
+  </si>
+  <si>
+    <t>Outliers are always biased and almost never true data</t>
+  </si>
+  <si>
+    <t>The highest score</t>
+  </si>
+  <si>
+    <t>Central tendency/ the average</t>
+  </si>
+  <si>
+    <t>Why is MRI popular?</t>
+  </si>
+  <si>
+    <t>Non-invasive, non-ionizing radiation</t>
+  </si>
+  <si>
+    <t>Good spatial resolution</t>
+  </si>
+  <si>
+    <t>Superior soft tissue contrast in vivo (can show difference in tissue type)</t>
+  </si>
+  <si>
+    <t>All of the above</t>
+  </si>
+  <si>
+    <t>Fundamentals of Neuroimaging Techniques [Notes from MSc course]</t>
+  </si>
+  <si>
+    <t>Set theory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set is collection of distinct items where order does not matter and there is no repetition. {} Elements of a set need not be related at all but MUST BE WELL DEFINED. Represented as a roster listing all elements one by one {each,item,separated,by,commas} or as a a set builder form {x:followed by the condition that x follows that acts as a filter}. </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iTZfATpm0Yk</t>
+  </si>
+  <si>
+    <t>Types of sets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finite set, Infinite set, Equal sets, Equivalent sets (same number of element), Singleton (one element), empty/nut set (no elements), subset and superset, power sets, universal set  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis for discrete math; also very common in coding  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follow several algebraic rules. The notations are extremely annoying but commonly used. Set notation, union (∪), intersection (∩), complement ('), Cartesian product (A × B), De Morgan Laws (describe how the complement of a set interacts with the union and intersection of sets.). Helpful to google 'set theory notation cheat sheet. </t>
+  </si>
+  <si>
+    <t>Intervals</t>
+  </si>
+  <si>
+    <t>A connected subset of numbers containing all numbers that lie between two designated endpoints a and b (where a &lt; b).</t>
+  </si>
+  <si>
+    <t>Open Interval (a, b), Closed Interval [a, b], Half-Open / Half-Closed Interval: Includes only one endpoint [a, b) or (a, b], Infinite Interval [a, ∞) or (-∞, b].</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zpln5ExhkyI?si=FCetaqTdXNPH_zlQ   ; https://www.geeksforgeeks.org/maths/absolute-value/</t>
+  </si>
+  <si>
+    <t>Absolute value</t>
+  </si>
+  <si>
+    <t>bsolute value of a number represents its distance from zero on the number line, regardless of direction. It is always non-negative</t>
+  </si>
+  <si>
+    <t>denote by |x|</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/52tpYl2tTqk?si=fuH3EUDmCFAeFrVI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explains how one set relates to another. Input set (domain) and output set (range). Sort of a machine that takes an input x and gives you exactly one output f(x). One input cannot give 2 outputs.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Has specific arithmetic rules that it follows. Especially with the second set. </t>
   </si>
 </sst>
 </file>
@@ -462,7 +552,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -531,12 +621,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -680,6 +807,46 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -697,34 +864,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -746,6 +885,10 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -962,121 +1105,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20" style="28" customWidth="1"/>
-    <col min="2" max="2" width="46" style="28" customWidth="1"/>
-    <col min="3" max="3" width="44.6328125" style="28" customWidth="1"/>
-    <col min="4" max="4" width="47.7265625" style="28" customWidth="1"/>
-    <col min="5" max="5" width="21.26953125" style="28" customWidth="1"/>
-    <col min="6" max="16384" width="12.6328125" style="26"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="23" customFormat="1" ht="15.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-    </row>
-    <row r="2" spans="1:5" s="23" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:5" s="25" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-    </row>
-    <row r="4" spans="1:5" ht="50" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="46" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-    </row>
-    <row r="7" spans="1:5" ht="50" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A6:XFD6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="10" customWidth="1"/>
@@ -1115,12 +1149,12 @@
       <c r="F2" s="17"/>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
       <c r="E3" s="13"/>
       <c r="F3" s="18"/>
     </row>
@@ -1157,211 +1191,413 @@
       <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="43"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="7" spans="1:6" s="50" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+    <row r="7" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="43"/>
+      <c r="F7" s="19"/>
+    </row>
+    <row r="8" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="43"/>
+      <c r="F8" s="19"/>
+    </row>
+    <row r="9" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="42"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="19"/>
+    </row>
+    <row r="10" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="43"/>
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A11" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="43"/>
+      <c r="F11" s="19"/>
+    </row>
+    <row r="12" spans="1:6" s="47" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-    </row>
-    <row r="8" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+    </row>
+    <row r="13" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D13" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="19"/>
-    </row>
-    <row r="9" spans="1:6" ht="50" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="E13" s="14"/>
+      <c r="F13" s="19"/>
+    </row>
+    <row r="14" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D14" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="19"/>
-    </row>
-    <row r="10" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="19"/>
-    </row>
-    <row r="11" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="19"/>
-    </row>
-    <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="19"/>
-    </row>
-    <row r="13" spans="1:6" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="9"/>
       <c r="E14" s="14"/>
       <c r="F14" s="19"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
+    <row r="15" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>34</v>
+      </c>
       <c r="E15" s="14"/>
       <c r="F15" s="19"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
+    <row r="16" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="E16" s="14"/>
       <c r="F16" s="19"/>
     </row>
-    <row r="17" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>66</v>
+    <row r="17" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="9"/>
+        <v>50</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="E17" s="14"/>
       <c r="F17" s="19"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="19"/>
+    <row r="18" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="D19" s="9"/>
       <c r="E19" s="14"/>
       <c r="F19" s="19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
+      <c r="A20" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
       <c r="F20" s="19"/>
     </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="19"/>
+    </row>
+    <row r="22" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="19"/>
+    </row>
+    <row r="23" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="19"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="19"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="19"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A7:XFD7"/>
-    <mergeCell ref="A13:XFD13"/>
+    <mergeCell ref="A12:XFD12"/>
+    <mergeCell ref="A18:XFD18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" xr:uid="{92139182-3192-4FD1-B073-C33397C80744}"/>
-    <hyperlink ref="D9" r:id="rId2" xr:uid="{D1A1E46E-289A-40F9-8E46-65C6381295A3}"/>
+    <hyperlink ref="D14" r:id="rId2" xr:uid="{D1A1E46E-289A-40F9-8E46-65C6381295A3}"/>
+    <hyperlink ref="D11" r:id="rId3" xr:uid="{32425B40-8980-4DFC-B5ED-4064E201972D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="44" fitToHeight="0" orientation="portrait" r:id="rId3"/>
+  <pageSetup scale="44" fitToHeight="0" orientation="portrait" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" style="28" customWidth="1"/>
+    <col min="2" max="2" width="46" style="28" customWidth="1"/>
+    <col min="3" max="3" width="44.6328125" style="28" customWidth="1"/>
+    <col min="4" max="4" width="47.7265625" style="28" customWidth="1"/>
+    <col min="5" max="5" width="21.26953125" style="28" customWidth="1"/>
+    <col min="6" max="16384" width="12.6328125" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="23" customFormat="1" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+    </row>
+    <row r="2" spans="1:5" s="23" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="24"/>
+    </row>
+    <row r="3" spans="1:5" s="25" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A3" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+    </row>
+    <row r="4" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="56" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A6" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+    </row>
+    <row r="7" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="56" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A8" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A6:XFD6"/>
+    <mergeCell ref="A8:XFD8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1383,14 +1619,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="32" customFormat="1" ht="13.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
     </row>
     <row r="2" spans="1:6" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
@@ -1409,14 +1645,14 @@
       <c r="F2" s="33"/>
     </row>
     <row r="3" spans="1:6" s="34" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
     </row>
     <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
@@ -1433,15 +1669,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="60" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="58" t="s">
+    <row r="7" spans="1:6" s="63" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A7" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1455,7 +1691,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C239A2E7-9F6A-46E7-89C3-299758E3487A}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.26953125" style="40" customWidth="1"/>
@@ -1513,17 +1749,51 @@
       <c r="B3" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="40" t="s">
         <v>82</v>
-      </c>
-      <c r="D3" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>84</v>
       </c>
       <c r="F3" s="40" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A4" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/GoldfishMemory.xlsx
+++ b/GoldfishMemory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manju\Desktop\Academia\website_portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF33FB4B-1A12-40DD-AC57-D00BA3FCC66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889E800C-97E5-4526-B44A-BDB032E68221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="212">
   <si>
     <t>Neuroscience</t>
   </si>
@@ -46,12 +46,6 @@
     <t>Resources</t>
   </si>
   <si>
-    <t xml:space="preserve">Eyetracking </t>
-  </si>
-  <si>
-    <t>High school math resources- which is apparently super relevant (I forgot everything)</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=OmJ-4B-mS-Y</t>
   </si>
   <si>
@@ -133,24 +127,12 @@
     <t xml:space="preserve">Essence of calculus </t>
   </si>
   <si>
-    <t>A little more intense for me. Clearly explained logic behind rules of calculus</t>
-  </si>
-  <si>
     <t xml:space="preserve">3B1B YT Channel </t>
   </si>
   <si>
     <t>Infamous 3B1B YT Channel that you will see throughout</t>
   </si>
   <si>
-    <t xml:space="preserve">Introduction to Eytracking </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preprocessing eyetracking data </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink detection </t>
-  </si>
-  <si>
     <t>Transcranial Focused Ultrasound</t>
   </si>
   <si>
@@ -292,9 +274,6 @@
     <t xml:space="preserve">It is not scary. </t>
   </si>
   <si>
-    <t>Outliers are always biased and almost never true data</t>
-  </si>
-  <si>
     <t>The highest score</t>
   </si>
   <si>
@@ -316,9 +295,6 @@
     <t>All of the above</t>
   </si>
   <si>
-    <t>Fundamentals of Neuroimaging Techniques [Notes from MSc course]</t>
-  </si>
-  <si>
     <t>Set theory</t>
   </si>
   <si>
@@ -371,13 +347,459 @@
   </si>
   <si>
     <t xml:space="preserve">Has specific arithmetic rules that it follows. Especially with the second set. </t>
+  </si>
+  <si>
+    <t>Rational Functions</t>
+  </si>
+  <si>
+    <t>Partial fraction decomposition</t>
+  </si>
+  <si>
+    <t>Exponentials</t>
+  </si>
+  <si>
+    <t>Logarithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euler's number </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Understanding Trignometry </t>
+  </si>
+  <si>
+    <t>In a quadratic equation, why cant a=0?</t>
+  </si>
+  <si>
+    <t>Equation becomes linear</t>
+  </si>
+  <si>
+    <t>No more roots, only one solution</t>
+  </si>
+  <si>
+    <t>No more parabola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outliers are always biased data </t>
+  </si>
+  <si>
+    <t>Outliers deviate from the normal gaussian curve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-calculus topic. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio of two polynomial functions f(x)= p(x)/q(x), where p &amp; q are polynomial and q(x) is not 0. Asymptotes (lines that a graph approaches but never touches). Discontinuities ('holes' in graph where a denominator hits zero. </t>
+  </si>
+  <si>
+    <t>High school math resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take a single fraction and separate it into smaller fractions, by factoring the denominator </t>
+  </si>
+  <si>
+    <t>Pre-calculus topic. Relevant for Laplace</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QKkdYW77xNI?si=7rbqLGwL9duAZaS3</t>
+  </si>
+  <si>
+    <t>Why is there no true exponential in the real physical world?</t>
+  </si>
+  <si>
+    <t>In real world, everything is a gaussian curve and a growth means a decay</t>
+  </si>
+  <si>
+    <t>None of the above</t>
+  </si>
+  <si>
+    <t>It becomes a logistic curve when nearing the population number/ end of finite resources.</t>
+  </si>
+  <si>
+    <t>The real world variables are chaotic and in true from do not follow any graph.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essential for modeling systems where the rate of change is directly proportional to the current size of the system. Laws of exponenets. Inflection point </t>
+  </si>
+  <si>
+    <r>
+      <t>Variable at the power [not the base] (a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)Exponential growth and decay</t>
+    </r>
+  </si>
+  <si>
+    <t>https://youtu.be/Kas0tIxDvrg?si=-xmGqocKnBIvLHZl ; https://youtu.be/LkhPRz7Hocg?si=w6dXiYWhLXCIrleC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information theory </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamental part of all communication; taking sections and putting it together to convey/understand something. Unit of message/information= bit.  </t>
+  </si>
+  <si>
+    <t>https://youtu.be/d9alWZRzBWk?si=jndG7ytNHb6y9Gd7 ; https://youtu.be/bkLHszLlH34?si=orA0ABEu94hFtvO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine learning statistics is based on data compression and the information theory. Shannon entropy and joint multivariate entropy. Relative entropy (Kullback-Beiber divergence). I have not understood these in detail now. But the video goes through all of this briefly. </t>
+  </si>
+  <si>
+    <t>https://youtu.be/zzu2POfYv0Y?si=JPr_Ei-xuxwPLbwD ; https://youtu.be/LCmnKWXCIfk?si=egk61nJkSG5K6dg_ ; https://youtu.be/sQ2ix7QcGwQ?si=e4-YH-qC1a44EEhl</t>
+  </si>
+  <si>
+    <r>
+      <t>Log</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>base</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Answer= Power [BAP]. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Natural log (Answer=infinity, base=e, 'ln') and common log (base=10). Change of base property to express one log with a different base (log</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x=log</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x/log</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>b)</t>
+    </r>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0QmSuIWAhhk?si=xlCW6d-b2DNQZGZj</t>
+  </si>
+  <si>
+    <t>its just everywhere apparently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e= 2.71828…... </t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZU-cIz8dvqU?si=yAxuYMHwK-jeP5LF ; https://youtu.be/YX2V3TjSeoo?si=dLvgypv5txpMzBTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Understanding everything as a right angle triangle--&gt; therefore all triangles --&gt; therefore all circle --&gt; therefore all waves. Very strict properties and rules. </t>
+  </si>
+  <si>
+    <t>Why compute inverse trignometric functions?</t>
+  </si>
+  <si>
+    <t>To get angle from ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To get a function of wave with 1 solution </t>
+  </si>
+  <si>
+    <t>To pinpoint direction in the graph</t>
+  </si>
+  <si>
+    <t>Wave parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radian is an angle measurement unit from the center of the circle based on an arc length equal to the radius (s=r). So, for full circle circumference as the arc length radian=2πr. Unit circle (r=1, therefore, c=2π). Inverse trignometric functions is to calculate the angle from the ratio and length [Principle branch of the wave for computing it as a function]. Also follow pythogorean identities, product sum rules, etc.  </t>
+  </si>
+  <si>
+    <t>https://youtu.be/9WZM68aVnGk?si=b6qUhWem8AbsKNrN ; https://youtu.be/0ORHDj3VEEY?si=kDOMyD2-G1U9nn18</t>
+  </si>
+  <si>
+    <t>Amplitude is the peak height of a wave from its center line. Wavelength is distance taken in retuning to the start point (lamba). Angular frequency is the rate of a wave's cycle in radians per unit time (ω = 2πf). Frequency (f=1/t) is the number of complete wave cycles per unit time. Period is time duration of a single wave cycle (t). Phase shift is the horizontal offset of a wave (φ- phase constant, measured in radian/degree)</t>
+  </si>
+  <si>
+    <t>Wave equation gives a the function of the wave to be calculated at any point in time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complex numbers </t>
+  </si>
+  <si>
+    <t>https://youtu.be/SP-YJe7Vldo?si=AHdLJHkpuSHeXx79 ; https://youtu.be/BZxZ_eEuJBM?si=I2mNYiTMk6s1Ej7Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Need to understand the algebraic properties of complex numbers. </t>
+  </si>
+  <si>
+    <r>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= -1. Equations with real and imaginary numbers is complex (z = a + bi)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://youtu.be/igJdDN-DPgA?si=5R2SrIvEHYwBD-st</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If g(x)&lt;/=f(x)&lt;/=h(x), If g(x) and h(x) both approach the exact same limit as x approaches a specific point, then the trapped function f(x) has no choice but to approach that same limit as well. </t>
+  </si>
+  <si>
+    <t>Squeeze/sandwich theorem</t>
+  </si>
+  <si>
+    <t>Calculating limit of a function that is difficult to evaluate directly by squeezing it between two other functions whose limits are easier to know. Fun to hear Sal (Khan academy) keep saying 'squeeze' repeatedly in the video.</t>
+  </si>
+  <si>
+    <t>epsilon-delta definition replaces vague phrases like "gets closer" with precise mathematical guarantees</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-ejyeII0i5c&amp;list=PL19E79A0638C8D449&amp;index=11</t>
+  </si>
+  <si>
+    <t>Epsilon-delta limit</t>
+  </si>
+  <si>
+    <t>Epsilon is defined as any number greater than 0 as a distance from the Limit we are approaching. Delta is the x value as a distance around 'a'. So if you give me an epsilon value of how close to the limit you want to be, I can give you the corresponding delta RANGE, such that f(x) within the epsilon that you specificed is guaranteed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l'Hôpital's rule </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using derivates to calculate limits that end up in indetermined form. </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PdSzruR5OeE</t>
+  </si>
+  <si>
+    <t>When the limit is indetermined form, L'Hôpital's Rule states that you can take the derivative of the numerator and the derivative of the denominator separately, and then try evaluating the limit again</t>
+  </si>
+  <si>
+    <t>Derivates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Differential calculus </t>
+  </si>
+  <si>
+    <t>slope of a tangent line. Rate of change at an instantenous moment. As d(t) is made to approach 0, the smaller difference, more 'instantenous'- slope of the tangent line is closer to that point alone.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=N2PpRnFqnqY ; 3B1B playlist 'paradox of der.'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very useful to vizualize. Watch simultaneously w other videos. </t>
+  </si>
+  <si>
+    <t>Shapes</t>
+  </si>
+  <si>
+    <t>Differential rules</t>
+  </si>
+  <si>
+    <t>3B1B 'essence of calculus' Ch. 3 &amp;4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power rule, sum rule, product rule, quotient rule, d(sine), chain rule </t>
+  </si>
+  <si>
+    <t>Rectangle/ square/ parallelogram= base x height; triangle = 1/2 x b x h; circle= π × r²; Trapezoid= ½ × (a + b) × h</t>
+  </si>
+  <si>
+    <t>Area of 2d shapes</t>
+  </si>
+  <si>
+    <t>Linear Algebra</t>
+  </si>
+  <si>
+    <t>Full course on Linear Algebra</t>
+  </si>
+  <si>
+    <t>Prof. Gilbert Strang MIT lecture series from 2005</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZK3O402wf1c?si=tW4gaaP43CJDfdDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was recommended this by a lot of peers and also my professor but it did not work for me. I did not watch but  leaving it here since it seems to have worked for a lot of others. </t>
+  </si>
+  <si>
+    <t>Essence of linear algebra</t>
+  </si>
+  <si>
+    <t>3B1B Playlist</t>
+  </si>
+  <si>
+    <t>https://youtube.com/playlist?list=PLZHQObOWTQDPD3MizzM2xVFitgF8hE_ab&amp;si=_wjdgAEzQn0ywvMx</t>
+  </si>
+  <si>
+    <t>Researching</t>
+  </si>
+  <si>
+    <t>Epistemology of neuroscience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How do we study neuroscience? How do we define a 'neural correlate' of cognitive process? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERY VERY VERY under recognized or under emphasized aspect of research. </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Wzi7pMhCQnw&amp;t=46s</t>
+  </si>
+  <si>
+    <t>Eyetracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction to eye tracking: hands on tutorial for students and practitioners </t>
+  </si>
+  <si>
+    <t>arXiv:2404.15435v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preprint worth reading for overview </t>
+  </si>
+  <si>
+    <t>Fun rabbithole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prof. Tobias Schlict has a really amazing collection of youtube videos that covers a variety of cognitive processes and neuroscientific research. </t>
+  </si>
+  <si>
+    <t>https://youtube.com/@tobiasschlicht935?si=Mlr4yF4baDiDxtqB</t>
+  </si>
+  <si>
+    <t>Neuroanatomy</t>
+  </si>
+  <si>
+    <t>Anatomy</t>
+  </si>
+  <si>
+    <t>https://youtube.com/playlist?list=PLYcLrRDaR8_cBHy0sWaCaLmOlJb9gzmA2&amp;si=VJBD3J6VVHWAtGn2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicosis Perfectionalis YT channel </t>
+  </si>
+  <si>
+    <t>Understanding signals from the brain</t>
+  </si>
+  <si>
+    <t>From Neuron to Brain Textbook (John G.Nicholls, A. Robert Martin, Bruce G. Wallace, Paul A.Fuchs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playlist for medical students. Informative but intense. Can watch whatever is relevant. There are so so many other YT videos that could work for you better.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommend investing in 1 good textbook. </t>
+  </si>
+  <si>
+    <t>no intro needed for 3B1B anymore</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -453,8 +875,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -551,8 +995,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -658,12 +1108,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -693,10 +1165,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -773,13 +1241,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -811,59 +1272,69 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -886,9 +1357,48 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1110,15 +1620,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" style="10" customWidth="1"/>
-    <col min="2" max="2" width="46" style="10" customWidth="1"/>
-    <col min="3" max="3" width="44.6328125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="64.81640625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="21.26953125" style="15" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="20"/>
+    <col min="1" max="1" width="20" style="9" customWidth="1"/>
+    <col min="2" max="2" width="46" style="9" customWidth="1"/>
+    <col min="3" max="3" width="44.6328125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="64.81640625" style="45" customWidth="1"/>
+    <col min="5" max="5" width="21.26953125" style="14" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" style="19"/>
     <col min="7" max="16384" width="12.6328125" style="3"/>
   </cols>
   <sheetData>
@@ -1128,9 +1638,9 @@
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="16"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -1139,346 +1649,929 @@
       <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="17"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="18"/>
+      <c r="A3" s="63" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="19"/>
+        <v>54</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" ht="50" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="18"/>
+    </row>
+    <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="39"/>
+      <c r="F6" s="18"/>
+    </row>
+    <row r="7" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="39"/>
+      <c r="F7" s="18"/>
+    </row>
+    <row r="8" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="38"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="39"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="39"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:6" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="39"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="39"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:6" ht="53" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" s="39"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="39"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:6" ht="100" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="39"/>
+      <c r="F18" s="18"/>
+    </row>
+    <row r="19" spans="1:6" ht="100" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="39"/>
+      <c r="F19" s="18"/>
+    </row>
+    <row r="20" spans="1:6" ht="27" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="39"/>
+      <c r="F20" s="18"/>
+    </row>
+    <row r="21" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="D21" s="47"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="18"/>
+    </row>
+    <row r="22" spans="1:6" s="64" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A22" s="64" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="41"/>
+      <c r="F23" s="18"/>
+    </row>
+    <row r="24" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="18"/>
+    </row>
+    <row r="25" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="19"/>
-    </row>
-    <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="19"/>
-    </row>
-    <row r="7" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="43"/>
-      <c r="F7" s="19"/>
-    </row>
-    <row r="8" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="43"/>
-      <c r="F8" s="19"/>
-    </row>
-    <row r="9" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="19"/>
-    </row>
-    <row r="10" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="43"/>
-      <c r="F10" s="19"/>
-    </row>
-    <row r="11" spans="1:6" ht="50" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="43"/>
-      <c r="F11" s="19"/>
-    </row>
-    <row r="12" spans="1:6" s="47" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-    </row>
-    <row r="13" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="30" t="s">
+      <c r="C25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="19"/>
-    </row>
-    <row r="14" spans="1:6" ht="50" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="19"/>
-    </row>
-    <row r="15" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="19"/>
-    </row>
-    <row r="16" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="9" t="s">
+      <c r="E25" s="13"/>
+      <c r="F25" s="18"/>
+    </row>
+    <row r="26" spans="1:6" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" s="39"/>
+      <c r="F26" s="18"/>
+    </row>
+    <row r="27" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27" s="39"/>
+      <c r="F27" s="18"/>
+    </row>
+    <row r="28" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A28" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" s="39"/>
+      <c r="F28" s="18"/>
+    </row>
+    <row r="29" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A29" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="E29" s="39"/>
+      <c r="F29" s="18"/>
+    </row>
+    <row r="30" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A30" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" s="39"/>
+      <c r="F30" s="18"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="38"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="18"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="38"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="18"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="38"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="18"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="38"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="18"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="38"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="18"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="38"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="18"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="38"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="18"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="38"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="18"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="38"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="18"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="38"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="18"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="38"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="18"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="38"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="18"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="38"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="18"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="38"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="18"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="38"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="18"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="38"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="18"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="38"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="18"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="38"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="18"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="38"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="18"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="38"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="18"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="38"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="18"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="38"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="18"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="38"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="18"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="38"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="18"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="38"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="18"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="38"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="18"/>
+    </row>
+    <row r="57" spans="1:6" s="65" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A57" s="65" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A58" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" s="54" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+    </row>
+    <row r="59" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A59" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="C59" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="D59" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="E59" s="39"/>
+      <c r="F59" s="18"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="38"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="18"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="38"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="18"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="38"/>
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="18"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="38"/>
+      <c r="B63" s="38"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="47"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="18"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="38"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="47"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="18"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="38"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="47"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="18"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="38"/>
+      <c r="B66" s="38"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="47"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="18"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="38"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="18"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="38"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="47"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="18"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="38"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="18"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="18"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="18"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="38"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="47"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="18"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="38"/>
+      <c r="B73" s="38"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="47"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="18"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="38"/>
+      <c r="B74" s="38"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="18"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="38"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="47"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="18"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="38"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="18"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="38"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="47"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="18"/>
+    </row>
+    <row r="78" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="65" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B79" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="19"/>
-    </row>
-    <row r="17" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="19"/>
-    </row>
-    <row r="18" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
+      <c r="C79" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="D79" s="40"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="18"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C80" s="8"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="18"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81" s="8"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="18"/>
+    </row>
+    <row r="82" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="A82" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="19"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="19"/>
-    </row>
-    <row r="22" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="19"/>
-    </row>
-    <row r="23" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="19"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="19"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="18"/>
+    </row>
+    <row r="83" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A83" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D83" s="7"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="18"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="18"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A12:XFD12"/>
-    <mergeCell ref="A18:XFD18"/>
+    <mergeCell ref="A22:XFD22"/>
+    <mergeCell ref="A78:XFD78"/>
+    <mergeCell ref="A57:XFD57"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" xr:uid="{92139182-3192-4FD1-B073-C33397C80744}"/>
-    <hyperlink ref="D14" r:id="rId2" xr:uid="{D1A1E46E-289A-40F9-8E46-65C6381295A3}"/>
-    <hyperlink ref="D11" r:id="rId3" xr:uid="{32425B40-8980-4DFC-B5ED-4064E201972D}"/>
+    <hyperlink ref="D25" r:id="rId2" xr:uid="{97F3D460-0449-4649-B7FC-847CEDB5FA4F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="44" fitToHeight="0" orientation="portrait" r:id="rId4"/>
+  <pageSetup scale="44" fitToHeight="0" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1487,115 +2580,173 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" style="28" customWidth="1"/>
-    <col min="2" max="2" width="46" style="28" customWidth="1"/>
-    <col min="3" max="3" width="44.6328125" style="28" customWidth="1"/>
-    <col min="4" max="4" width="47.7265625" style="28" customWidth="1"/>
-    <col min="5" max="5" width="21.26953125" style="28" customWidth="1"/>
-    <col min="6" max="16384" width="12.6328125" style="26"/>
+    <col min="1" max="1" width="20" style="27" customWidth="1"/>
+    <col min="2" max="2" width="46" style="27" customWidth="1"/>
+    <col min="3" max="3" width="44.6328125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="47.7265625" style="27" customWidth="1"/>
+    <col min="5" max="5" width="21.26953125" style="27" customWidth="1"/>
+    <col min="6" max="16384" width="12.6328125" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="23" customFormat="1" ht="15.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:6" s="22" customFormat="1" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-    </row>
-    <row r="2" spans="1:5" s="23" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+    </row>
+    <row r="2" spans="1:6" s="22" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:5" s="25" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-    </row>
-    <row r="4" spans="1:5" ht="50" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="E2" s="23"/>
+    </row>
+    <row r="3" spans="1:6" s="24" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A3" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="69"/>
+    </row>
+    <row r="4" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="28" t="s">
+      <c r="C4" s="26" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="56" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="D4" s="27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A6" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+    </row>
+    <row r="7" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="53" customFormat="1" ht="25" x14ac:dyDescent="0.25">
+      <c r="A8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="51"/>
+      <c r="F8" s="52"/>
+    </row>
+    <row r="9" spans="1:6" s="53" customFormat="1" ht="25" x14ac:dyDescent="0.25">
+      <c r="A9" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-    </row>
-    <row r="7" spans="1:5" ht="50" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="C9" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="D9" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="56" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="52"/>
+    </row>
+    <row r="10" spans="1:6" s="75" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A10" s="73" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+    </row>
+    <row r="11" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>210</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A6:XFD6"/>
-    <mergeCell ref="A8:XFD8"/>
+    <mergeCell ref="A10:XFD10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1606,84 +2757,119 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" style="36" customWidth="1"/>
-    <col min="2" max="2" width="46" style="36" customWidth="1"/>
-    <col min="3" max="3" width="44.6328125" style="36" customWidth="1"/>
-    <col min="4" max="4" width="39.7265625" style="36" customWidth="1"/>
-    <col min="5" max="5" width="21.26953125" style="36" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="36"/>
-    <col min="7" max="16384" width="12.6328125" style="37"/>
+    <col min="1" max="1" width="23.54296875" style="33" customWidth="1"/>
+    <col min="2" max="2" width="46" style="33" customWidth="1"/>
+    <col min="3" max="3" width="44.6328125" style="33" customWidth="1"/>
+    <col min="4" max="4" width="39.7265625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="21.26953125" style="33" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" style="33"/>
+    <col min="7" max="16384" width="12.6328125" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="32" customFormat="1" ht="13.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:6" s="29" customFormat="1" ht="13.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-    </row>
-    <row r="2" spans="1:6" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+    </row>
+    <row r="2" spans="1:6" s="29" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-    </row>
-    <row r="3" spans="1:6" s="34" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A3" s="59" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="3" spans="1:6" s="31" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A3" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
     </row>
     <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>40</v>
+      <c r="A4" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="63" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
+      <c r="A6" s="32"/>
+    </row>
+    <row r="7" spans="1:6" s="62" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A7" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+    </row>
+    <row r="9" spans="1:6" s="62" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A9" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+    </row>
+    <row r="10" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>198</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A7:XFD7"/>
+    <mergeCell ref="A9:XFD9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1691,109 +2877,175 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C239A2E7-9F6A-46E7-89C3-299758E3487A}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.26953125" style="40" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" style="40" customWidth="1"/>
-    <col min="3" max="4" width="26.36328125" style="40" customWidth="1"/>
-    <col min="5" max="5" width="28.6328125" style="40" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" style="40" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="40"/>
+    <col min="1" max="1" width="33.26953125" style="37" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" style="37" customWidth="1"/>
+    <col min="3" max="4" width="26.36328125" style="37" customWidth="1"/>
+    <col min="5" max="5" width="28.6328125" style="37" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="37" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="38" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:6" s="35" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="38" t="s">
+      <c r="D2" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="38" t="s">
+      <c r="F2" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="39" t="s">
+      <c r="B3" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="F2" s="39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="F3" s="37" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B4" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="40" t="s">
+      <c r="C4" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="40" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="D4" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="C5" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="D5" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="E5" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="39" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>96</v>
+      <c r="F5" s="36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7" s="36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/GoldfishMemory.xlsx
+++ b/GoldfishMemory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manju\Desktop\Academia\website_portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889E800C-97E5-4526-B44A-BDB032E68221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB8D84D-3E47-43BE-B62E-BA79541A0E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Maths" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="218">
   <si>
     <t>Neuroscience</t>
   </si>
@@ -741,9 +741,6 @@
     <t xml:space="preserve">How do we study neuroscience? How do we define a 'neural correlate' of cognitive process? </t>
   </si>
   <si>
-    <t xml:space="preserve">VERY VERY VERY under recognized or under emphasized aspect of research. </t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=Wzi7pMhCQnw&amp;t=46s</t>
   </si>
   <si>
@@ -793,6 +790,27 @@
   </si>
   <si>
     <t>no intro needed for 3B1B anymore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERY VERY under emphasized aspect of research in my opinion. </t>
+  </si>
+  <si>
+    <t>Neuromodulation</t>
+  </si>
+  <si>
+    <t>Transcranial Alternating Current Stimulation (tACS)</t>
+  </si>
+  <si>
+    <t>Transcranial Magnetic Stimulation</t>
+  </si>
+  <si>
+    <t>Transcranial direct-current stimulation</t>
+  </si>
+  <si>
+    <t>Deep Brain Stimulation (DBS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philosopher in cognitive sciences. Makes you think intuitively about neuroscience. </t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1399,6 +1417,30 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2320,7 +2362,7 @@
         <v>189</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D59" s="47" t="s">
         <v>190</v>
@@ -2709,7 +2751,7 @@
     </row>
     <row r="10" spans="1:6" s="75" customFormat="1" ht="13" x14ac:dyDescent="0.25">
       <c r="A10" s="73" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B10" s="74"/>
       <c r="C10" s="74"/>
@@ -2719,27 +2761,27 @@
     </row>
     <row r="11" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="26" t="s">
-        <v>208</v>
-      </c>
       <c r="C12" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -2757,7 +2799,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.54296875" style="33" customWidth="1"/>
@@ -2812,30 +2854,33 @@
       <c r="B4" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>194</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="C5" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>201</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="32"/>
     </row>
-    <row r="7" spans="1:6" s="62" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" s="76" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="60" t="s">
-        <v>36</v>
+        <v>212</v>
       </c>
       <c r="B7" s="61"/>
       <c r="C7" s="61"/>
@@ -2843,25 +2888,70 @@
       <c r="E7" s="61"/>
       <c r="F7" s="61"/>
     </row>
-    <row r="9" spans="1:6" s="62" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="60" t="s">
+    <row r="8" spans="1:6" s="79" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="83" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="82" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="80"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+    </row>
+    <row r="10" spans="1:6" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="82" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="80"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+    </row>
+    <row r="11" spans="1:6" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="82" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="80"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+    </row>
+    <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A12" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+    </row>
+    <row r="13" spans="1:6" s="62" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A13" s="60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+    </row>
+    <row r="14" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-    </row>
-    <row r="10" spans="1:6" ht="50" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="C14" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" s="33" t="s">
         <v>197</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2869,7 +2959,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A7:XFD7"/>
-    <mergeCell ref="A9:XFD9"/>
+    <mergeCell ref="A13:XFD13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GoldfishMemory.xlsx
+++ b/GoldfishMemory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manju\Desktop\Academia\website_portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB8D84D-3E47-43BE-B62E-BA79541A0E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18209C1-4534-4A38-89D2-6C2BF7F20A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,9 +404,6 @@
   </si>
   <si>
     <t>Why is there no true exponential in the real physical world?</t>
-  </si>
-  <si>
-    <t>In real world, everything is a gaussian curve and a growth means a decay</t>
   </si>
   <si>
     <t>None of the above</t>
@@ -812,6 +809,9 @@
   <si>
     <t xml:space="preserve">Philosopher in cognitive sciences. Makes you think intuitively about neuroscience. </t>
   </si>
+  <si>
+    <t>In real world, everything is a gaussian curve and a growth is always followed by a decay</t>
+  </si>
 </sst>
 </file>
 
@@ -829,6 +829,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -836,16 +837,19 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1354,6 +1358,70 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1372,74 +1440,10 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1742,7 +1746,7 @@
       <c r="E5" s="13"/>
       <c r="F5" s="18"/>
     </row>
-    <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>11</v>
       </c>
@@ -1822,16 +1826,16 @@
     </row>
     <row r="11" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="C11" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="38" t="s">
         <v>135</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>136</v>
       </c>
       <c r="E11" s="39"/>
       <c r="F11" s="18"/>
@@ -1863,7 +1867,7 @@
         <v>120</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E13" s="39"/>
       <c r="F13" s="18"/>
@@ -1889,13 +1893,13 @@
         <v>110</v>
       </c>
       <c r="B15" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="47" t="s">
         <v>132</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>133</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="18"/>
@@ -1905,13 +1909,13 @@
         <v>111</v>
       </c>
       <c r="B16" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="38" t="s">
-        <v>140</v>
-      </c>
       <c r="D16" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E16" s="39"/>
       <c r="F16" s="18"/>
@@ -1921,13 +1925,13 @@
         <v>112</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E17" s="39"/>
       <c r="F17" s="18"/>
@@ -1937,58 +1941,58 @@
         <v>113</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E18" s="39"/>
       <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:6" ht="100" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B19" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="C19" s="38" t="s">
-        <v>155</v>
-      </c>
       <c r="D19" s="47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E19" s="39"/>
       <c r="F19" s="18"/>
     </row>
     <row r="20" spans="1:6" ht="27" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="47" t="s">
         <v>156</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>157</v>
       </c>
       <c r="E20" s="39"/>
       <c r="F20" s="18"/>
     </row>
     <row r="21" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B21" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="38" t="s">
         <v>181</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>182</v>
       </c>
       <c r="D21" s="47"/>
       <c r="E21" s="39"/>
@@ -2023,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>32</v>
@@ -2049,78 +2053,78 @@
     </row>
     <row r="26" spans="1:6" ht="62.5" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>163</v>
-      </c>
       <c r="D26" s="38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E26" s="39"/>
       <c r="F26" s="18"/>
     </row>
     <row r="27" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A27" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="B27" s="38" t="s">
-        <v>167</v>
-      </c>
       <c r="C27" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="D27" s="38" t="s">
         <v>164</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>165</v>
       </c>
       <c r="E27" s="39"/>
       <c r="F27" s="18"/>
     </row>
     <row r="28" spans="1:6" ht="50" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="B28" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="C28" s="38" t="s">
+      <c r="D28" s="38" t="s">
         <v>169</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>170</v>
       </c>
       <c r="E28" s="39"/>
       <c r="F28" s="18"/>
     </row>
     <row r="29" spans="1:6" ht="50" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="B29" s="38" t="s">
+      <c r="D29" s="38" t="s">
         <v>174</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>175</v>
       </c>
       <c r="E29" s="39"/>
       <c r="F29" s="18"/>
     </row>
     <row r="30" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A30" s="38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B30" s="38"/>
       <c r="C30" s="38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E30" s="39"/>
       <c r="F30" s="18"/>
@@ -2335,37 +2339,37 @@
     </row>
     <row r="57" spans="1:6" s="65" customFormat="1" ht="13" x14ac:dyDescent="0.25">
       <c r="A57" s="65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="50" x14ac:dyDescent="0.25">
       <c r="A58" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="B58" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="B58" s="54" t="s">
+      <c r="C58" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="D58" s="55" t="s">
         <v>185</v>
-      </c>
-      <c r="C58" s="54" t="s">
-        <v>187</v>
-      </c>
-      <c r="D58" s="55" t="s">
-        <v>186</v>
       </c>
       <c r="E58" s="18"/>
       <c r="F58" s="18"/>
     </row>
     <row r="59" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B59" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="B59" s="38" t="s">
+      <c r="C59" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="D59" s="47" t="s">
         <v>189</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="D59" s="47" t="s">
-        <v>190</v>
       </c>
       <c r="E59" s="39"/>
       <c r="F59" s="18"/>
@@ -2751,7 +2755,7 @@
     </row>
     <row r="10" spans="1:6" s="75" customFormat="1" ht="13" x14ac:dyDescent="0.25">
       <c r="A10" s="73" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B10" s="74"/>
       <c r="C10" s="74"/>
@@ -2761,27 +2765,27 @@
     </row>
     <row r="11" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="B12" s="26" t="s">
-        <v>207</v>
-      </c>
       <c r="C12" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2812,14 +2816,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="29" customFormat="1" ht="13.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
     </row>
     <row r="2" spans="1:6" s="29" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
@@ -2838,120 +2842,120 @@
       <c r="F2" s="30"/>
     </row>
     <row r="3" spans="1:6" s="31" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A3" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
+      <c r="A3" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
     </row>
     <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="C4" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>193</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="33" t="s">
         <v>199</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="C5" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>200</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="32"/>
     </row>
-    <row r="7" spans="1:6" s="76" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="60" t="s">
+    <row r="7" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A7" s="80" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+    </row>
+    <row r="8" spans="1:6" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="62" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="60" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="61" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+    </row>
+    <row r="10" spans="1:6" s="60" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-    </row>
-    <row r="8" spans="1:6" s="79" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="83" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="82" t="s">
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+    </row>
+    <row r="11" spans="1:6" s="60" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="61" t="s">
         <v>214</v>
       </c>
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-    </row>
-    <row r="10" spans="1:6" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="82" t="s">
-        <v>213</v>
-      </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-    </row>
-    <row r="11" spans="1:6" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="82" t="s">
-        <v>215</v>
-      </c>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
     </row>
     <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-    </row>
-    <row r="13" spans="1:6" s="62" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
-        <v>195</v>
-      </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+    </row>
+    <row r="13" spans="1:6" s="83" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A13" s="80" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
     </row>
     <row r="14" spans="1:6" ht="50" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="33" t="s">
         <v>196</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3103,16 +3107,16 @@
         <v>126</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C7" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="36" t="s">
         <v>127</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>128</v>
       </c>
       <c r="F7" s="36" t="s">
         <v>66</v>
@@ -3120,16 +3124,16 @@
     </row>
     <row r="8" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="C8" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="D8" s="36" t="s">
         <v>149</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>150</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>89</v>

--- a/GoldfishMemory.xlsx
+++ b/GoldfishMemory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manju\Desktop\Academia\website_portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18209C1-4534-4A38-89D2-6C2BF7F20A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87196FC9-4902-4DD7-AFB7-46D70227552D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="227">
   <si>
     <t>Neuroscience</t>
   </si>
@@ -804,13 +804,40 @@
     <t>Transcranial direct-current stimulation</t>
   </si>
   <si>
-    <t>Deep Brain Stimulation (DBS)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Philosopher in cognitive sciences. Makes you think intuitively about neuroscience. </t>
   </si>
   <si>
     <t>In real world, everything is a gaussian curve and a growth is always followed by a decay</t>
+  </si>
+  <si>
+    <t>doi: 10.3389/fnins.2017.00641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tDCS is a non-invasive method, allowing for the reversible modulation of activity in particular brain regions. </t>
+  </si>
+  <si>
+    <t>form of neuromodulation that uses a steady current, low-intensity DC electricity between 1 - 2 mA delivered through electrodes.</t>
+  </si>
+  <si>
+    <t>Emerging technique that can reach deeper brain surfaces</t>
+  </si>
+  <si>
+    <t>doi: 10.1038/s41467-023-40998-0.</t>
+  </si>
+  <si>
+    <t>Blink detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One of the biggest artefact. </t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.3758/s13428-017-1008-1?fromPaywallRec=false</t>
+  </si>
+  <si>
+    <t>Laplace</t>
+  </si>
+  <si>
+    <t>Fourier</t>
   </si>
 </sst>
 </file>
@@ -1364,9 +1391,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1376,9 +1400,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1440,11 +1461,18 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1705,12 +1733,12 @@
       <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
       <c r="E3" s="12"/>
       <c r="F3" s="17"/>
     </row>
@@ -1746,7 +1774,7 @@
       <c r="E5" s="13"/>
       <c r="F5" s="18"/>
     </row>
-    <row r="6" spans="1:6" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>11</v>
       </c>
@@ -1998,8 +2026,8 @@
       <c r="E21" s="39"/>
       <c r="F21" s="18"/>
     </row>
-    <row r="22" spans="1:6" s="64" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
+    <row r="22" spans="1:6" s="62" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A22" s="62" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2337,8 +2365,8 @@
       <c r="E56" s="39"/>
       <c r="F56" s="18"/>
     </row>
-    <row r="57" spans="1:6" s="65" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A57" s="65" t="s">
+    <row r="57" spans="1:6" s="63" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A57" s="63" t="s">
         <v>182</v>
       </c>
     </row>
@@ -2518,8 +2546,8 @@
       <c r="E77" s="39"/>
       <c r="F77" s="18"/>
     </row>
-    <row r="78" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="65" t="s">
+    <row r="78" spans="1:6" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="63" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2626,7 +2654,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="27" customWidth="1"/>
@@ -2662,13 +2690,13 @@
       <c r="E2" s="23"/>
     </row>
     <row r="3" spans="1:6" s="24" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
     </row>
     <row r="4" spans="1:6" ht="50" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
@@ -2698,14 +2726,14 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A6" s="70" t="s">
+    <row r="6" spans="1:6" s="70" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A6" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
     </row>
     <row r="7" spans="1:6" ht="50" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
@@ -2753,38 +2781,58 @@
       <c r="E9" s="51"/>
       <c r="F9" s="52"/>
     </row>
-    <row r="10" spans="1:6" s="75" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A10" s="73" t="s">
+    <row r="10" spans="1:6" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="83" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="52"/>
+    </row>
+    <row r="11" spans="1:6" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="52"/>
+    </row>
+    <row r="12" spans="1:6" s="73" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+      <c r="A12" s="71" t="s">
         <v>202</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-    </row>
-    <row r="11" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+    </row>
+    <row r="13" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B13" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C13" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D13" s="27" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+    <row r="14" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B14" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C14" s="26" t="s">
         <v>208</v>
       </c>
     </row>
@@ -2792,7 +2840,7 @@
   <mergeCells count="3">
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A6:XFD6"/>
-    <mergeCell ref="A10:XFD10"/>
+    <mergeCell ref="A12:XFD12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2816,14 +2864,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="29" customFormat="1" ht="13.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
     </row>
     <row r="2" spans="1:6" s="29" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
@@ -2842,14 +2890,14 @@
       <c r="F2" s="30"/>
     </row>
     <row r="3" spans="1:6" s="31" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
     </row>
     <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
@@ -2873,7 +2921,7 @@
         <v>199</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D5" s="33" t="s">
         <v>200</v>
@@ -2882,80 +2930,95 @@
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="32"/>
     </row>
-    <row r="7" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="80" t="s">
+    <row r="7" spans="1:6" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A7" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-    </row>
-    <row r="8" spans="1:6" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="62" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="60" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="61" t="s">
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+    </row>
+    <row r="8" spans="1:6" s="59" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="60" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-    </row>
-    <row r="10" spans="1:6" s="60" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="61" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+    </row>
+    <row r="9" spans="1:6" s="59" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="60" t="s">
         <v>212</v>
       </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-    </row>
-    <row r="11" spans="1:6" s="60" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="61" t="s">
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+    </row>
+    <row r="10" spans="1:6" s="59" customFormat="1" ht="38" x14ac:dyDescent="0.3">
+      <c r="A10" s="60" t="s">
         <v>214</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-    </row>
-    <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A12" s="56" t="s">
+      <c r="B10" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" s="60" t="s">
+        <v>217</v>
+      </c>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+    </row>
+    <row r="11" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A11" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-    </row>
-    <row r="13" spans="1:6" s="83" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A13" s="80" t="s">
+      <c r="C11" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+    </row>
+    <row r="12" spans="1:6" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A12" s="78" t="s">
         <v>194</v>
       </c>
-      <c r="B13" s="81"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-    </row>
-    <row r="14" spans="1:6" ht="50" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+      <c r="B12" s="79"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+    </row>
+    <row r="13" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C13" s="33" t="s">
         <v>197</v>
       </c>
+      <c r="D13" s="33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>223</v>
+      </c>
       <c r="D14" s="33" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2963,7 +3026,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A7:XFD7"/>
-    <mergeCell ref="A13:XFD13"/>
+    <mergeCell ref="A12:XFD12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3110,7 +3173,7 @@
         <v>129</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>128</v>
